--- a/1 NUMISTA.AI/output_antigravity_2_0_commands_reference (1).xlsx
+++ b/1 NUMISTA.AI/output_antigravity_2_0_commands_reference (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6af8775946bee8a7/Documents/1 NUMISTA.AI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericd\Documents\MyVertexProject\1 NUMISTA.AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBE806A-D1E7-449F-B2D7-899F4190CBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="4596" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19980" yWindow="7152" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Command Reference Matrix" sheetId="1" r:id="rId1"/>
